--- a/backend/data/acts/act_aliases.xlsx
+++ b/backend/data/acts/act_aliases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,78 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POCSO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POCSO Act</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>POCSO 2012</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>POCSO Act 2012</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>POCSO Act, 2012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>The Protection of Children from Sexual Offences Act, 2012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>THE PROTECTION OF CHILDREN FROM SEXUAL OFFENCES (POCSO) ACT, 2012</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
